--- a/output/2026-09-03_19_Italia_Basilicata_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-03_19_Italia_Basilicata_ATEX_Equipment-Services.xlsx
@@ -510,7 +510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,6 @@
           <t>0975 354253</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Pagina 'assistenza-tecnica' del sito indicizzata con contenuto relativo a verifiche di sicurezza ambientale secondo Direttiva ATEX 94/9/CE, nell'ambito dei servizi di assistenza tecnica per apparecchiature industriali offerti a clienti terzi (noleggio/vendita gruppi elettrogeni, compressori, per settore Oil&amp;Gas Val d'Agri). B2B, non cliente finale. Email non trovata/confermata: lasciata vuota nonostante presente (vuota) anche nell'input originale.</t>
@@ -548,7 +547,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -590,7 +589,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -620,7 +619,6 @@
           <t>0835 238925</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Pagine prodotto indicizzate confermano vendita di articoli ATEX-certificati: avvolgitubo ZECA AM86 con marcatura EX II 2 GD c IIB T6/T85°C conforme a direttiva 2014/34/UE e norme EN 13463-1/EN 13463-5, oltre a DPI con certificazioni ATEX/antistatiche. Distributore/rivenditore B2B di attrezzature per zone Ex. Email non trovata/confermata: lasciata vuota.</t>
@@ -628,7 +626,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
